--- a/DAY 1/Suvam Nath Test Report.xlsx
+++ b/DAY 1/Suvam Nath Test Report.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\capgemini OOPS QUESTIONS\sprint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF4787C-F155-4837-AAA0-1049279C0922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42122DFD-F28D-46A0-91BB-935A8B01F4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{94427D90-7315-4F36-8219-E2CBD7BBE3A9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{94427D90-7315-4F36-8219-E2CBD7BBE3A9}"/>
   </bookViews>
   <sheets>
     <sheet name="User Story" sheetId="1" r:id="rId1"/>
     <sheet name="Test Scenarios" sheetId="2" r:id="rId2"/>
+    <sheet name="Test cases" sheetId="3" r:id="rId3"/>
+    <sheet name="RTM" sheetId="4" r:id="rId4"/>
+    <sheet name="Defect Report" sheetId="5" r:id="rId5"/>
+    <sheet name="Summary" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="476">
   <si>
     <t>Issue Type</t>
   </si>
@@ -311,12 +315,1343 @@
 3. To validate that selecting Buy under Commercial shows both Property Type and Availability dropdowns
 </t>
   </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Test Scenario</t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Test Condition</t>
+  </si>
+  <si>
+    <t>Test Case Steps</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result Iteration 1</t>
+  </si>
+  <si>
+    <t>Status
+Iteration 1</t>
+  </si>
+  <si>
+    <t>Actual Result Iteration 2
+(to be updated only if test case failed in Iteration 1)</t>
+  </si>
+  <si>
+    <t>Status
+Iteration 2
+(to be updated only if test case failed in Iteration 1)</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Req: Reference</t>
+  </si>
+  <si>
+    <t>&lt;Sequence number&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Identify test scenarios&gt;</t>
+  </si>
+  <si>
+    <t>&lt;This cell specifies the state a system and its environment must be in before this specific test&gt;</t>
+  </si>
+  <si>
+    <t>&lt;This cell describes what to test for i.e. the condition which is being tested for&gt;</t>
+  </si>
+  <si>
+    <t>&lt;This cell describes how to test i.e. the detailed testing procedure&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Mention test data to be used&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Describe the expected test result&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Describe the actual test result after execution of test cases. In case screenshots need to be attached&gt;</t>
+  </si>
+  <si>
+    <t>Status of the test case whether it got passed/failed/Hold in iteration 1.</t>
+  </si>
+  <si>
+    <t>&lt;Describe the actual test result after execution of test cases second time. In case screenshots need to be attached&gt;</t>
+  </si>
+  <si>
+    <t>New status of test case after it failed in Iteration 1)</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_01</t>
+  </si>
+  <si>
+    <t>User has opened nobroker.in on a supported browser</t>
+  </si>
+  <si>
+    <t>To validate that user can select a valid city from the dropdown</t>
+  </si>
+  <si>
+    <t>Selected city appears in the search window or box.</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_02</t>
+  </si>
+  <si>
+    <t>User has opened nobroker.in and has selected a city</t>
+  </si>
+  <si>
+    <t>To validate that user on putting any location name on the search bar shows auto suggestions and can select one</t>
+  </si>
+  <si>
+    <t>1. Open nobroker.in
+2. Click on the city dropdown on the homepage
+3. Select a city (e.g., Mumbai)</t>
+  </si>
+  <si>
+    <t>City: Mumbai</t>
+  </si>
+  <si>
+    <t>1.Click on the input field where the localities or landmarks have been mentioned.
+2. Type a locality name like (e.g., "Bori")
+3.Observe the auto-suggestions
+4. Click any suggestion from the list</t>
+  </si>
+  <si>
+    <t>Locality:Borivali West, Mumbai,Maharashtra,India</t>
+  </si>
+  <si>
+    <t>Auto-suggestions appears and user chooses from those options</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_03</t>
+  </si>
+  <si>
+    <t>To validate that after clicking on the search button, we are navigated to the results page</t>
+  </si>
+  <si>
+    <t>1. Select city and locality
+2. Click the search button</t>
+  </si>
+  <si>
+    <t>City: Mumbai
+Locality: Borivali</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_04</t>
+  </si>
+  <si>
+    <t>User has selected a city and locality on nobroker.in</t>
+  </si>
+  <si>
+    <t>User has opened nobroker.in without selecting any locality</t>
+  </si>
+  <si>
+    <t>To validate that clicking the search button without filling the location leads to error showing that location needs to be filled</t>
+  </si>
+  <si>
+    <t>1. Open nobroker.in
+2. Do not select any locality
+3. Click the search button</t>
+  </si>
+  <si>
+    <t>No input provided</t>
+  </si>
+  <si>
+    <t>User is not navigated to results and error message is thrown</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_05</t>
+  </si>
+  <si>
+    <t>User is on the Buy tab and has selected Full House</t>
+  </si>
+  <si>
+    <t>To validate that BHK type dropdown, Property Status and New Builder Projects checkbox appear for Full House and the search results appear for it</t>
+  </si>
+  <si>
+    <t>1. City:Mumbai
+2. Location: Borivali
+3. BHK type : 1BHK
+4. Property Status: Ready
+5. Checked New Builder Projects</t>
+  </si>
+  <si>
+    <t>1. Select city
+2. Select locality
+3. Select the Full House option
+4. Click 1BHK under BHK Type dropdown
+5. Select Property Status dropdown
+6. TickMark the New Builder Projects option
+7. Click on search button</t>
+  </si>
+  <si>
+    <t>User is navigated to results page with those filters applied</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_06</t>
+  </si>
+  <si>
+    <t>User is on the Rent tab and has selected Full House</t>
+  </si>
+  <si>
+    <t>To validate that BHK type dropdown, and clicking on the search button provides result</t>
+  </si>
+  <si>
+    <t>1. Select city
+2. Select locality
+3. Select the Rent option
+4. Click 1BHK under BHK Type dropdown
+5. Click on search button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. City:Mumbai
+2. Location: Borivali
+3. Rent type selected
+3. BHK type : 1BHK
+</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_07</t>
+  </si>
+  <si>
+    <t>User is on the Rent tab and has selected PG/Hostel or flatmates option</t>
+  </si>
+  <si>
+    <t>To validate the Tenant type and the Room type drop downand clicking on search button yields results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. City:Mumbai
+2. Location: Borivali
+3. Rent type selected
+3. Select PG/Hostel or Flatmates
+4. Tenant type: Male
+5. Room type: Double sharing
+</t>
+  </si>
+  <si>
+    <t>1. Select city
+2. Select locality
+3. Select the Rent option
+4. Select PG/Hostel or Flatmates
+5. Select tenant type
+6. Select Room type
+7. Click on search button</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_08</t>
+  </si>
+  <si>
+    <t>User is on the nobroker.in homepage</t>
+  </si>
+  <si>
+    <t>Tab: Commercial</t>
+  </si>
+  <si>
+    <t>Verify Commercial Tab – Rent &amp; Buy Options with Search Flow</t>
+  </si>
+  <si>
+    <t>To validate that when the user selects the Commercial tab, both Rent and Buy options are displayed with their respective fields, and search functionality navigates to the results page correctly.</t>
+  </si>
+  <si>
+    <t>1. Click on the Commercial tab
+2. Verify that Rent and Buy radio buttons are displayed
+3. Select "Rent" option and observe available property type fields
+4. Select "Buy" option and observe property type and availability fields
+5. Enter valid search inputs (location/property type)
+6. Click on the Search button</t>
+  </si>
+  <si>
+    <t>1. Rent and Buy radio buttons should be displayed under Commercial tab
+2. On selecting Rent → relevant property type options should be displayed
+3. On selecting Buy → property type and availability options should be displayed
+4. On clicking Search → user should be navigated to the results page with relevant commercial listings</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_09</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_20</t>
+  </si>
+  <si>
+    <t>User is on the rental property listing page on nobroker.in</t>
+  </si>
+  <si>
+    <t>To validate filtering rental properties by BHK type</t>
+  </si>
+  <si>
+    <t>1. Navigate to rental listings
+2. Click BHK filter
+3. Select "2BHK"
+4. Observe results</t>
+  </si>
+  <si>
+    <t>BHK: 2BHK</t>
+  </si>
+  <si>
+    <t>Only 2BHK rental properties are displayed in the results</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_21</t>
+  </si>
+  <si>
+    <t>User is on the rental property listing page</t>
+  </si>
+  <si>
+    <t>To validate filtering properties using the rent range slider</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_10</t>
+  </si>
+  <si>
+    <t>1. Navigate to rental listings
+2. Adjust rent range slider to min: 6 lacs and max: 36 lacs
+3. Observe results</t>
+  </si>
+  <si>
+    <t>Rent Range: 6 lacs - 36 lacs</t>
+  </si>
+  <si>
+    <t>Only properties within 6 lacs and 36 lacs rent range are displayed</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_22</t>
+  </si>
+  <si>
+    <t>To validate filtering by property status (Under Construction or Ready)</t>
+  </si>
+  <si>
+    <t>1. Navigate to rental listings
+2. Select "Ready" under Property Status filter
+3. Observe results</t>
+  </si>
+  <si>
+    <t>Status: Ready</t>
+  </si>
+  <si>
+    <t>Only Ready properties are shown in the results</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_11</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_25</t>
+  </si>
+  <si>
+    <t>To validate filtering by Furnishing status (Full,Semi or None)</t>
+  </si>
+  <si>
+    <t>1. Click Furnishing
+2. Select " Full "
+3. Observe results</t>
+  </si>
+  <si>
+    <t>Availability: Full</t>
+  </si>
+  <si>
+    <t>Only properties with full furnished are displayed</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_27</t>
+  </si>
+  <si>
+    <t>To validate filtering by property type</t>
+  </si>
+  <si>
+    <t>1. Click Property Type filter
+2. Select "Apartment"
+3. Observe results</t>
+  </si>
+  <si>
+    <t>Property Type: Apartment</t>
+  </si>
+  <si>
+    <t>Only Apartment listings are displayed</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_12</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_13</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_29</t>
+  </si>
+  <si>
+    <t>To validate filtering by parking availability</t>
+  </si>
+  <si>
+    <t>1. Click Parking filter
+2. Select "4-Wheeler"
+3. Observe results</t>
+  </si>
+  <si>
+    <t>Parking: 4-Wheeler</t>
+  </si>
+  <si>
+    <t>Only properties with 4-Wheeler parking are displayed</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_14</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_31</t>
+  </si>
+  <si>
+    <t>User is logged in and on the property listing page</t>
+  </si>
+  <si>
+    <t>To validate that clicking "Get Owner Details" displays the owner's contact information</t>
+  </si>
+  <si>
+    <t>1. Log in to nobroker.in
+2. Navigate to a property listing
+3. Click "Get Owner Details" button</t>
+  </si>
+  <si>
+    <t>Logged-in user</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_15</t>
+  </si>
+  <si>
+    <t>Owner's contact information is sent to Whatsapp or email</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_32</t>
+  </si>
+  <si>
+    <t>To validate that clicking the heart icon adds the property to the shortlist</t>
+  </si>
+  <si>
+    <t>1. Log in to nobroker.in
+2. Navigate to a property listing
+3. Click the heart (wishlist) icon on a property card</t>
+  </si>
+  <si>
+    <t>Property is added to the shortlist and heart icon turns active/filled</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_33</t>
+  </si>
+  <si>
+    <t>User is logged in and has shortlisted at least one property</t>
+  </si>
+  <si>
+    <t>To validate that shortlisted properties are visible in the wishlist section</t>
+  </si>
+  <si>
+    <t>1. Log in to nobroker.in
+2. Navigate to the Shortlist/Wishlist section
+3. Observe listed properties</t>
+  </si>
+  <si>
+    <t>Logged-in user with shortlisted property</t>
+  </si>
+  <si>
+    <t>All shortlisted properties are displayed in the wishlist section</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_16</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_17</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_34</t>
+  </si>
+  <si>
+    <t>User is logged in and has a property already shortlisted</t>
+  </si>
+  <si>
+    <t>To validate that clicking the heart icon again removes the property from the shortlist</t>
+  </si>
+  <si>
+    <t>1. Log in to nobroker.in
+2. Navigate to a shortlisted property
+3. Click the heart icon again</t>
+  </si>
+  <si>
+    <t>Property is removed from the shortlist and heart icon turns inactive/unfilled</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_18</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_35</t>
+  </si>
+  <si>
+    <t>User is NOT logged in (guest/anonymous)</t>
+  </si>
+  <si>
+    <t>1. Open nobroker.in without logging in
+2. Navigate to a property listing
+3. Click "Get Owner Details" button</t>
+  </si>
+  <si>
+    <t>Guest/logged-out user</t>
+  </si>
+  <si>
+    <t>To validate that a guest user clicking "Get Owner Details" is prompted to log in</t>
+  </si>
+  <si>
+    <t>User is redirected to a page where login with phone number prompt is displayed</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_19</t>
+  </si>
+  <si>
+    <t>1. Open nobroker.in
+2. Click on the locality input field
+3. Type a random invalid string (e.g., "xyzabc123")
+4. Observe the auto-suggestion dropdown</t>
+  </si>
+  <si>
+    <t>Locality: xyzabc123</t>
+  </si>
+  <si>
+    <t>To validate that entering a random invalid/non-existing locality shows no suggestions or an error</t>
+  </si>
+  <si>
+    <t>User has clicked the Rent tab and selected PG/Hostel</t>
+  </si>
+  <si>
+    <t>1. Click the Rent tab
+2. Select "PG/Hostel"
+3. Observe the available filter fields</t>
+  </si>
+  <si>
+    <t>Option: PG/Hostel</t>
+  </si>
+  <si>
+    <t>BHK type dropdown is NOT displayed; only Tenant Type and Room Type dropdowns are shown</t>
+  </si>
+  <si>
+    <t>Verify PG For (Gender) Filter</t>
+  </si>
+  <si>
+    <t>Verify Room Type Filter</t>
+  </si>
+  <si>
+    <t>Verify Rent Range Filter</t>
+  </si>
+  <si>
+    <t>Verify Preferred For Filter (Student / Professional)</t>
+  </si>
+  <si>
+    <t>Verify Food Included Filter (Breakfast / Lunch / Dinner)</t>
+  </si>
+  <si>
+    <t>1. To validate selecting "Breakfast" shows PGs that include breakfast
+2. To validate selecting "Lunch" shows PGs that include lunch
+3. To validate selecting "Dinner" shows PGs that include dinner
+4. To validate selecting all three food options returns only PGs with all meals included</t>
+  </si>
+  <si>
+    <t>Verify Show Only Filter (With Photos / Attached Bathroom)</t>
+  </si>
+  <si>
+    <t>Verify Combined / Multiple Filters Applied Together</t>
+  </si>
+  <si>
+    <t>Verify Reset Filters Functionality</t>
+  </si>
+  <si>
+    <t>1. To validate selecting "Male" shows only Boys PG listings
+2. To validate selecting "Female" shows only Girls PG listings
+3. To validate selecting "Anyone" shows all PG listings regardless of gender
+4. To validate that results do NOT mix Male and Female PGs when a specific gender is selected</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_08</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_09</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_08</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. To validate selecting "Single Room" shows only single room PGs
+2. To validate selecting "Double Room" shows only double sharing PGs
+3. To validate selecting "Triple Room" shows only triple sharing PGs
+4. To validate selecting "Four Room" shows only 4-sharing PGs
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. To validate that adjusting the rent range slider filters PGs within the selected range
+2. To validate that the rent range slider minimum defaults to ₹0 and maximum to ₹1 Lac
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. To validate selecting "Student" shows only PGs that prefer students
+2. To validate selecting "Professional" shows only PGs that prefer working professionals
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. To validate that "With Photos" filter shows only PG listings that have photos attached
+2. To validate that "Attached Bathroom" filter shows only PGs with attached bathroom
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. To validate that applying Gender + Room Type + Rent Range together returns correctly refined results
+2. To validate that applying all available filters simultaneously returns only matching listings
+</t>
+  </si>
+  <si>
+    <t>1. To validate that clicking "Reset" clears all applied filters and restores full listing results
+2. To validate that clicking Reset when no filters are applied does not cause any error or unexpected behaviour</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_10</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_11</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_12</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_13</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_14</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_15</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_10</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_11</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_12</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_13</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_14</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_15</t>
+  </si>
+  <si>
+    <t>User is on the PG/Hostel listing page (e.g., Navapada, Mumbai) with the Filters panel visible</t>
+  </si>
+  <si>
+    <t>To validate that selecting "Male" under PG For shows only Boys PG listings</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. In Filters panel, under "PG For" select "Male"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>PG For: Male</t>
+  </si>
+  <si>
+    <t>Only Boys PG / Male PG listings are displayed; no Female-only PGs appear in results</t>
+  </si>
+  <si>
+    <t>User is on the PG/Hostel listing page with the Filters panel visible</t>
+  </si>
+  <si>
+    <t>To validate that selecting "Female" under PG For shows only Girls PG listings</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. In Filters panel, under "PG For" select "Female"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>PG For: Female</t>
+  </si>
+  <si>
+    <t>Only Girls PG / Female PG listings are displayed; no Male-only PGs appear in results</t>
+  </si>
+  <si>
+    <t>To validate that selecting "Anyone" under PG For shows all PG listings regardless of gender</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. In Filters panel, under "PG For" select "Anyone"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>PG For: Anyone</t>
+  </si>
+  <si>
+    <t>All PG listings (Male, Female, and Mixed) are displayed in the results</t>
+  </si>
+  <si>
+    <t>User is on the PG/Hostel listing page and has selected "Male" under PG For</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. In Filters panel, under "PG For" select "Male"
+3. Review all result cards and verify none are tagged as Female-only</t>
+  </si>
+  <si>
+    <t>No Female-only PG listings appear in the results; all results are Male or Mixed PGs only</t>
+  </si>
+  <si>
+    <t>To validate that selecting "Single Room" shows only single occupancy PG listings</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Room Type", check "Single Room"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>Room Type: Single Room</t>
+  </si>
+  <si>
+    <t>Only PG listings offering Single Room occupancy are displayed in results</t>
+  </si>
+  <si>
+    <t>To validate that selecting "Double Room" shows only double sharing PG listings</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Room Type", check "Double Room"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>Room Type: Double Room</t>
+  </si>
+  <si>
+    <t>Only PG listings offering Double sharing rooms are displayed in results</t>
+  </si>
+  <si>
+    <t>[Negative] To validate that selecting "Four Room" does NOT show Single, Double or Triple room PGs</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Room Type", check "Four Room" only
+3. Verify none of the results show Single, Double or Triple Room PGs</t>
+  </si>
+  <si>
+    <t>Room Type: Four Room only</t>
+  </si>
+  <si>
+    <t>No Single, Double or Triple Room PG listings appear; only 4-sharing PGs are shown</t>
+  </si>
+  <si>
+    <t>To validate that adjusting the rent range slider filters PGs within the selected price range</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Adjust the rent range slider to min: ₹3,000 and max: ₹10,000
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>Rent Range: ₹3,000 – ₹10,000</t>
+  </si>
+  <si>
+    <t>Only PG listings with rent/month between ₹3,000 and ₹10,000 are displayed</t>
+  </si>
+  <si>
+    <t>To validate that selecting "Student" shows only PGs that prefer students</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Preferred For", check "Student"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>Preferred For: Student</t>
+  </si>
+  <si>
+    <t>Only PG listings tagged as suitable for Students are displayed in results</t>
+  </si>
+  <si>
+    <t>To validate that selecting "Professional" shows only PGs that prefer working professionals</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Preferred For", check "Professional"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>Preferred For: Professional</t>
+  </si>
+  <si>
+    <t>Only PG listings tagged as suitable for Working Professionals are displayed in results</t>
+  </si>
+  <si>
+    <t>User is on the PG/Hostel listing page and has selected "Professional" under Preferred For</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Preferred For", check "Professional" only
+3. Verify all result cards — none should be tagged as Student-only</t>
+  </si>
+  <si>
+    <t>Preferred For: Professional only</t>
+  </si>
+  <si>
+    <t>No Student-only PG listings appear in the results</t>
+  </si>
+  <si>
+    <t>To validate that selecting "BreakFast" shows only PGs that include breakfast</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Food Included", check "BreakFast"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>Food Included: Breakfast</t>
+  </si>
+  <si>
+    <t>Only PG listings that include Breakfast in their facilities are displayed</t>
+  </si>
+  <si>
+    <t>To validate that selecting "Lunch" shows only PGs that include lunch</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Food Included", check "Lunch"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>Food Included: Lunch</t>
+  </si>
+  <si>
+    <t>Only PG listings that include Lunch in their facilities are displayed</t>
+  </si>
+  <si>
+    <t>To validate that selecting "Dinner" shows only PGs that include dinner</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Food Included", check "Dinner"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>Food Included: Dinner</t>
+  </si>
+  <si>
+    <t>Only PG listings that include Dinner in their facilities are displayed</t>
+  </si>
+  <si>
+    <t>To validate that "With Photos" filter shows only PG listings that have photos attached</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Show Only", click "With Photos"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>Show Only: With Photos</t>
+  </si>
+  <si>
+    <t>All displayed PG listings have at least one photo; listings without photos are hidden</t>
+  </si>
+  <si>
+    <t>To validate that "Attached Bathroom" filter shows only PGs that have an attached bathroom</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Show Only", click "Attached Bathroom"
+3. Observe the listing results</t>
+  </si>
+  <si>
+    <t>Show Only: Attached Bathroom</t>
+  </si>
+  <si>
+    <t>Only PG listings with an attached bathroom are displayed; PGs with shared bathrooms are hidden</t>
+  </si>
+  <si>
+    <t>User is on the PG/Hostel listing page and has applied "With Photos" filter</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Under "Show Only", click "With Photos"
+3. Scroll through all results and verify no listing is photo-less</t>
+  </si>
+  <si>
+    <t>No photo-less PG listings appear in the results</t>
+  </si>
+  <si>
+    <t>To validate that applying Gender + Room Type + Rent Range together returns correctly refined results</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Set PG For: Male
+3. Set Room Type: Double Room
+4. Set Rent Range: ₹5,000 – ₹15,000
+5. Observe the listing results</t>
+  </si>
+  <si>
+    <t>PG For: Male, Room Type: Double Room, Rent: ₹5,000 – ₹15,000</t>
+  </si>
+  <si>
+    <t>Only Male PGs with Double Room availability and rent between ₹5,000–₹15,000 per month are displayed</t>
+  </si>
+  <si>
+    <t>To validate that applying all available filters simultaneously returns only matching listings</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Set PG For: Male
+3. Set Room Type: Single Room
+4. Set Preferred For: Student
+5. Set Food Included: Breakfast + Dinner
+6. Set Show Only: With Photos + Attached Bathroom
+7. Observe results</t>
+  </si>
+  <si>
+    <t>PG For: Male, Room: Single, Student, Food: Breakfast+Dinner, With Photos, Attached Bathroom</t>
+  </si>
+  <si>
+    <t>Only listings that match ALL applied filter criteria simultaneously are displayed</t>
+  </si>
+  <si>
+    <t>User is on the PG/Hostel listing page and has applied one or more filters</t>
+  </si>
+  <si>
+    <t>To validate that clicking "Reset" clears all applied filters and restores full listing results</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Apply filters: PG For: Male, Room Type: Double Room, Food: Breakfast
+3. Note the filtered results count
+4. Click the "Reset" button
+5. Observe results after reset</t>
+  </si>
+  <si>
+    <t>Filters Applied: Male + Double Room + Breakfast</t>
+  </si>
+  <si>
+    <t>All applied filters are cleared; the filter panel resets to default state and the full unfiltered listing is restored</t>
+  </si>
+  <si>
+    <t>User is on the PG/Hostel listing page with NO filters applied</t>
+  </si>
+  <si>
+    <t>1. Navigate to PG/Hostel listings on nobroker.in
+2. Do NOT apply any filter
+3. Click the "Reset" button
+4. Observe page behaviour and listings</t>
+  </si>
+  <si>
+    <t>Filters Applied: None</t>
+  </si>
+  <si>
+    <t>Page behaves normally with no errors or unexpected behaviour; all listings remain unchanged</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_23</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_24</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_26</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_28</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_30</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_36</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_37</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_38</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_39</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_40</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_41</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_42</t>
+  </si>
+  <si>
+    <t>PG For (Gender) Filter</t>
+  </si>
+  <si>
+    <t>Select "Male" radio button to filter and show only Boys PG listings</t>
+  </si>
+  <si>
+    <t>Select "Female" radio button to filter and show only Girls PG listings</t>
+  </si>
+  <si>
+    <t>Select "Anyone" radio button to show all PG listings regardless of gender</t>
+  </si>
+  <si>
+    <t>Story 7</t>
+  </si>
+  <si>
+    <t>Room Type Filter</t>
+  </si>
+  <si>
+    <t>Check "Single Room" checkbox to display only single occupancy PG listings</t>
+  </si>
+  <si>
+    <t>Check "Double Room" checkbox to display only double sharing PG listings</t>
+  </si>
+  <si>
+    <t>Check "Triple Room" checkbox to display only triple sharing PG listings</t>
+  </si>
+  <si>
+    <t>Check "Four Room" checkbox to display only 4-sharing PG listings</t>
+  </si>
+  <si>
+    <t>Story 13</t>
+  </si>
+  <si>
+    <t>Rent Range Filter</t>
+  </si>
+  <si>
+    <t>Adjust the rent range slider to filter PGs within a selected price range</t>
+  </si>
+  <si>
+    <t>Verify the rent range slider defaults to ₹0 minimum and ₹1 Lac maximum on page load</t>
+  </si>
+  <si>
+    <t>Preferred For Filter (Student / Professional)</t>
+  </si>
+  <si>
+    <t>Check "Student" checkbox to show only PG listings that prefer students</t>
+  </si>
+  <si>
+    <t>Check "Professional" checkbox to show only PG listings that prefer working professionals</t>
+  </si>
+  <si>
+    <t>Food Included Filter (Breakfast / Lunch / Dinner)</t>
+  </si>
+  <si>
+    <t>Check "BreakFast" checkbox to show only PGs that include breakfast</t>
+  </si>
+  <si>
+    <t>Check "Lunch" checkbox to show only PGs that include lunch</t>
+  </si>
+  <si>
+    <t>Check "Dinner" checkbox to show only PGs that include dinner</t>
+  </si>
+  <si>
+    <t>Check all three food options (Breakfast + Lunch + Dinner) to show only PGs with all meals included</t>
+  </si>
+  <si>
+    <t>Show Only Filter (With Photos / Attached Bathroom)</t>
+  </si>
+  <si>
+    <t>Click "With Photos" button to show only PG listings that have at least one photo attached</t>
+  </si>
+  <si>
+    <t>Click "Attached Bathroom" button to show only PGs that have an attached bathroom</t>
+  </si>
+  <si>
+    <t>Combined / Multiple Filters Applied Together</t>
+  </si>
+  <si>
+    <t>Apply Gender + Room Type + Rent Range filters simultaneously and verify results are correctly refined</t>
+  </si>
+  <si>
+    <t>Apply all available filters simultaneously and verify only fully matching listings appear</t>
+  </si>
+  <si>
+    <t>Reset Filters Functionality</t>
+  </si>
+  <si>
+    <t>Click "Reset" button after applying filters to clear all filters and restore the full listing results</t>
+  </si>
+  <si>
+    <t>Story 6</t>
+  </si>
+  <si>
+    <t>Story 8</t>
+  </si>
+  <si>
+    <t>Story 9</t>
+  </si>
+  <si>
+    <t>Story 10</t>
+  </si>
+  <si>
+    <t>Story 11</t>
+  </si>
+  <si>
+    <t>Story 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that results do NOT mix Male-only and Female-only PGs when a specific gender is selected </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click "Reset" when no filters are applied and verify no error or unexpected behaviour occurs </t>
+  </si>
+  <si>
+    <t>User is taken to the results page where list of properties in Borivali is shown</t>
+  </si>
+  <si>
+    <t>User is taken to the results page where properties related to Borivali is displayed</t>
+  </si>
+  <si>
+    <t>Based on the given filters, properties are displayed</t>
+  </si>
+  <si>
+    <t>To validate that BHK type dropdown does NOT appear when PG/Hostel is selected</t>
+  </si>
+  <si>
+    <t>Male PG are displayed</t>
+  </si>
+  <si>
+    <t>Female PG displayed</t>
+  </si>
+  <si>
+    <t>Photos shows PG least one photo</t>
+  </si>
+  <si>
+    <t>Bathroom shows PGs are displayed</t>
+  </si>
+  <si>
+    <t>Reset all filters state</t>
+  </si>
+  <si>
+    <t>To validate that results do NOT mix Male and Female PGs when Male filter is selected</t>
+  </si>
+  <si>
+    <t>results are male PGs</t>
+  </si>
+  <si>
+    <t>Single Room occupancy are displayed in results</t>
+  </si>
+  <si>
+    <t>Double sharing rooms are displayed in results</t>
+  </si>
+  <si>
+    <t>only 4-sharing PGs are shown</t>
+  </si>
+  <si>
+    <t>PG with rent/month between the price range are displayed</t>
+  </si>
+  <si>
+    <t>To validate that Student-only PGs do NOT appear when Professional filter is selected</t>
+  </si>
+  <si>
+    <t>Any type of tenant are allowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> To validate that PG listings without photos do NOT appear when "With Photos" filter is applied</t>
+  </si>
+  <si>
+    <t>Boys PG list Is displayed alongwith the list for anyone too</t>
+  </si>
+  <si>
+    <t>Available PG both for boys and anyone are displayed</t>
+  </si>
+  <si>
+    <t>To validate that clicking "Reset" when no filters are applied does not cause any error or unexpected behaviour</t>
+  </si>
+  <si>
+    <t>Owner's contact information is displayed</t>
+  </si>
+  <si>
+    <t>Property is added to the shortlist and heart icon turns active/filled and a alert message about the product getting added to the wishlist is displayed</t>
+  </si>
+  <si>
+    <t>User is redirected to the login page</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>BR_ID</t>
+  </si>
+  <si>
+    <t>TR_ID</t>
+  </si>
+  <si>
+    <t>TS_ID</t>
+  </si>
+  <si>
+    <t>TC_ID</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>DR_ID</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_01</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_02</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_03</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_04</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_13</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_14</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_05</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_06</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_07</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_08</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_09</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_10</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_11</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_12</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_15</t>
+  </si>
+  <si>
+    <t>Defect Id.</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Defect Summary</t>
+  </si>
+  <si>
+    <t>Defect Priority</t>
+  </si>
+  <si>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>TEST EXECUTION SUMMARY</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Total Cases</t>
+  </si>
+  <si>
+    <t>Total Passed</t>
+  </si>
+  <si>
+    <t>Total Failed</t>
+  </si>
+  <si>
+    <t>Total Executed</t>
+  </si>
+  <si>
+    <t>Pass Percentage</t>
+  </si>
+  <si>
+    <t>Fail Percentage</t>
+  </si>
+  <si>
+    <t>Completion Percentage</t>
+  </si>
+  <si>
+    <t>NoBroker.in</t>
+  </si>
+  <si>
+    <t>Property Search</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>Buy Tab</t>
+  </si>
+  <si>
+    <t>Rent Tab</t>
+  </si>
+  <si>
+    <t>Commercial Tab</t>
+  </si>
+  <si>
+    <t>PG Gender Filter</t>
+  </si>
+  <si>
+    <t>Preferred For</t>
+  </si>
+  <si>
+    <t>Food Included</t>
+  </si>
+  <si>
+    <t>Show Only Filter</t>
+  </si>
+  <si>
+    <t>Combined Filters</t>
+  </si>
+  <si>
+    <t>Reset Filters</t>
+  </si>
+  <si>
+    <t>Rental Filters</t>
+  </si>
+  <si>
+    <t>Adv Filters</t>
+  </si>
+  <si>
+    <t>Owner &amp; Shortlist</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-suggestions appears </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,8 +1693,80 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF7F3F00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F3F00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Candara"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,8 +1820,55 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B183"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB6C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -437,6 +1891,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -444,34 +1987,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -481,6 +2002,193 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{D1AFDDC6-42B5-4A98-A03A-8FAD8F4FD474}"/>
@@ -796,7 +2504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D8DAB5-F88D-49FA-8B10-566C97F055C6}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -815,299 +2523,627 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:3" s="8" customFormat="1" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="14"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="C2" s="43"/>
+    </row>
+    <row r="3" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="15"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="C3" s="23"/>
+    </row>
+    <row r="4" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="8" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="35" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="36"/>
+    </row>
+    <row r="10" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>360</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>363</v>
+      </c>
+      <c r="C15" s="36"/>
+    </row>
+    <row r="16" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>364</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>366</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>367</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>369</v>
+      </c>
+      <c r="C21" s="36"/>
+    </row>
+    <row r="22" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>371</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="36"/>
+    </row>
+    <row r="26" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>373</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>374</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="34" t="s">
+        <v>388</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>375</v>
+      </c>
+      <c r="C29" s="36"/>
+    </row>
+    <row r="30" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>376</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>377</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>378</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>379</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="34" t="s">
+        <v>362</v>
+      </c>
+      <c r="B35" s="35" t="s">
+        <v>380</v>
+      </c>
+      <c r="C35" s="36"/>
+    </row>
+    <row r="36" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="38" t="s">
+        <v>382</v>
+      </c>
+      <c r="C37" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="34" t="s">
+        <v>389</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="C39" s="36"/>
+    </row>
+    <row r="40" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>384</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="38" t="s">
+        <v>385</v>
+      </c>
+      <c r="C41" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="34" t="s">
+        <v>390</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="C43" s="36"/>
+    </row>
+    <row r="44" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="38" t="s">
+        <v>387</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="38" t="s">
+        <v>395</v>
+      </c>
+      <c r="C45" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:3" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:3" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="1:3" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="B50" s="29" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="51" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B51" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C51" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="52" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B52" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C52" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="7" t="s">
+    <row r="53" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="54" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="B54" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="16"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="C54" s="23"/>
+    </row>
+    <row r="55" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B55" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C55" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+    <row r="56" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B56" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C56" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+    <row r="57" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B57" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C57" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+    <row r="58" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B58" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C58" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+    <row r="59" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B59" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C59" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="7" t="s">
+    <row r="60" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="B61" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="16"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="C61" s="23"/>
+    </row>
+    <row r="62" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B62" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C62" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+    <row r="63" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B63" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C63" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+    <row r="64" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B64" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C64" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+    <row r="65" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B65" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C65" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+    <row r="66" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B66" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C66" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+    <row r="67" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B67" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C67" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+    <row r="68" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B68" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C68" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+    <row r="69" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B69" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C69" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="7" t="s">
+    <row r="70" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="28" t="s">
+        <v>368</v>
+      </c>
+      <c r="B71" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="15"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+      <c r="C71" s="23"/>
+    </row>
+    <row r="72" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B72" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C72" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    <row r="73" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B73" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C73" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+    <row r="74" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B74" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C74" s="32" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1119,7 +3155,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08C5B4A0-C25E-4E1E-BB83-E285A1F8E72A}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
@@ -1131,166 +3167,3293 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="5">
         <v>5</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="4" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="5">
         <v>5</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="5">
         <v>4</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="5">
         <v>3</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:6" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="24">
+        <v>4</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="24">
+        <v>4</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="24">
+        <v>2</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="24">
+        <v>2</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="24">
+        <v>4</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="24">
+        <v>2</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="24">
+        <v>2</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="24">
+        <v>2</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E14" s="5">
         <v>5</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F14" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+    <row r="15" spans="1:6" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="5">
+        <v>6</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="5">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC29E54-1D54-40AA-8C35-102A6D3F9E33}">
+  <dimension ref="A1:M44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.77734375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="25.5546875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="24.44140625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="23" style="8" customWidth="1"/>
+    <col min="11" max="11" width="21.33203125" style="8" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="16.77734375" style="8" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" spans="1:13" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="I3" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="14" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="I4" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="I5" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I6" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="23" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="I7" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="144" x14ac:dyDescent="0.3">
+      <c r="A8" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="I8" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="I9" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="53" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="H10" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="I10" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J10" s="51"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="52" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="I11" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="243.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="I12" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J12" s="17"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I13" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J13" s="19"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J14" s="19"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="44" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I15" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J15" s="19"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="I16" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J16" s="19"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A17" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="I17" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J17" s="19"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="I18" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J18" s="19"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A19" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="I19" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A20" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J20" s="19"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="I21" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J21" s="19"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="44" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>405</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="I22" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J22" s="26"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="23" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="I23" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J23" s="19"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="23" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A24" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J24" s="19"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="23" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="44" t="s">
+        <v>346</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I25" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="23" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="44" t="s">
+        <v>347</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I26" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J26" s="19"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="23" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A27" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="I27" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J27" s="19"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="23" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="44" t="s">
+        <v>348</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="I28" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J28" s="19"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="23" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>411</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="I29" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J29" s="26"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="23" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A30" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="I30" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J30" s="19"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="23" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A31" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="I31" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J31" s="19"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="23" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A32" s="44" t="s">
+        <v>350</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="I32" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J32" s="19"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="23" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A33" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="I33" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J33" s="19"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="23" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A34" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I34" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J34" s="19"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="53" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>326</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>413</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>327</v>
+      </c>
+      <c r="F35" s="52" t="s">
+        <v>320</v>
+      </c>
+      <c r="G35" s="51" t="s">
+        <v>328</v>
+      </c>
+      <c r="H35" s="51" t="s">
+        <v>328</v>
+      </c>
+      <c r="I35" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J35" s="51"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="51"/>
+      <c r="M35" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="23" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="I36" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J36" s="19"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="23" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="I37" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J37" s="19"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="23" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="44" t="s">
+        <v>351</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="I38" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J38" s="19"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="23" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="48" t="s">
+        <v>352</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>416</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>343</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>345</v>
+      </c>
+      <c r="H39" s="26" t="s">
+        <v>345</v>
+      </c>
+      <c r="I39" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J39" s="26"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A40" s="44" t="s">
+        <v>353</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="I40" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J40" s="19"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="44" t="s">
+        <v>354</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="I41" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J41" s="19"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="44" t="s">
+        <v>355</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="I42" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J42" s="19"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="I43" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J43" s="19"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="I44" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="J44" s="19"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7BF8A5-4F15-42CB-ADF9-9465AAB7E167}">
+  <dimension ref="A1:F58"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="54" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>425</v>
+      </c>
+      <c r="F1" s="54" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="75" t="s">
+        <v>427</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F2" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F3" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="78"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F4" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="78"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F5" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="76"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="59"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+    </row>
+    <row r="8" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="55" t="s">
+        <v>429</v>
+      </c>
+      <c r="B8" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F8" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="59"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+    </row>
+    <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="75" t="s">
+        <v>430</v>
+      </c>
+      <c r="B10" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="78"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="76"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="57" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="59"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+    </row>
+    <row r="14" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="55" t="s">
+        <v>431</v>
+      </c>
+      <c r="B14" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>162</v>
+      </c>
+      <c r="E14" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="59"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+    </row>
+    <row r="16" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="75" t="s">
+        <v>432</v>
+      </c>
+      <c r="B16" s="77" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="77" t="s">
+        <v>252</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F16" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="78"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F17" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="76"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="57" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="59"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+    </row>
+    <row r="20" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="75" t="s">
+        <v>433</v>
+      </c>
+      <c r="B20" s="77" t="s">
+        <v>259</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>253</v>
+      </c>
+      <c r="D20" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F20" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="78"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="E21" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F21" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="76"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="57" t="s">
+        <v>207</v>
+      </c>
+      <c r="E22" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F22" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="59"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+    </row>
+    <row r="24" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="75" t="s">
+        <v>434</v>
+      </c>
+      <c r="B24" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="E24" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F24" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="78"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="E25" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F25" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="78"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F26" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="76"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="57" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F27" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="59"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+    </row>
+    <row r="29" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="75" t="s">
+        <v>435</v>
+      </c>
+      <c r="B29" s="77" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="19">
-        <v>6</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="D29" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F29" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="78"/>
+      <c r="B30" s="78"/>
+      <c r="C30" s="78"/>
+      <c r="D30" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="E30" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F30" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="76"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="57" t="s">
+        <v>346</v>
+      </c>
+      <c r="E31" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F31" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="59"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+    </row>
+    <row r="33" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="55" t="s">
+        <v>436</v>
+      </c>
+      <c r="B33" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="19">
-        <v>5</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>79</v>
-      </c>
+      <c r="D33" s="57" t="s">
+        <v>347</v>
+      </c>
+      <c r="E33" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F33" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="59"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+    </row>
+    <row r="35" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="75" t="s">
+        <v>437</v>
+      </c>
+      <c r="B35" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="C35" s="77" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F35" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="78"/>
+      <c r="B36" s="78"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="57" t="s">
+        <v>348</v>
+      </c>
+      <c r="E36" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F36" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="76"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="E37" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F37" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="59"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+    </row>
+    <row r="39" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="75" t="s">
+        <v>438</v>
+      </c>
+      <c r="B39" s="77" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" s="77" t="s">
+        <v>240</v>
+      </c>
+      <c r="D39" s="57" t="s">
+        <v>349</v>
+      </c>
+      <c r="E39" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F39" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="78"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="E40" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F40" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="76"/>
+      <c r="B41" s="76"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="57" t="s">
+        <v>350</v>
+      </c>
+      <c r="E41" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F41" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="59"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+    </row>
+    <row r="43" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75" t="s">
+        <v>439</v>
+      </c>
+      <c r="B43" s="77" t="s">
+        <v>255</v>
+      </c>
+      <c r="C43" s="77" t="s">
+        <v>249</v>
+      </c>
+      <c r="D43" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="E43" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F43" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="78"/>
+      <c r="B44" s="78"/>
+      <c r="C44" s="78"/>
+      <c r="D44" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="E44" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F44" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="76"/>
+      <c r="B45" s="76"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="E45" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F45" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="59"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+    </row>
+    <row r="47" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="75" t="s">
+        <v>440</v>
+      </c>
+      <c r="B47" s="77" t="s">
+        <v>256</v>
+      </c>
+      <c r="C47" s="77" t="s">
+        <v>250</v>
+      </c>
+      <c r="D47" s="57" t="s">
+        <v>209</v>
+      </c>
+      <c r="E47" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F47" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="76"/>
+      <c r="B48" s="76"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F48" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="59"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+    </row>
+    <row r="50" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="75" t="s">
+        <v>441</v>
+      </c>
+      <c r="B50" s="77" t="s">
+        <v>257</v>
+      </c>
+      <c r="C50" s="77" t="s">
+        <v>251</v>
+      </c>
+      <c r="D50" s="57" t="s">
+        <v>351</v>
+      </c>
+      <c r="E50" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F50" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="76"/>
+      <c r="B51" s="76"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="57" t="s">
+        <v>352</v>
+      </c>
+      <c r="E51" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F51" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="59"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+    </row>
+    <row r="53" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="75" t="s">
+        <v>442</v>
+      </c>
+      <c r="B53" s="77" t="s">
+        <v>260</v>
+      </c>
+      <c r="C53" s="77" t="s">
+        <v>254</v>
+      </c>
+      <c r="D53" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="E53" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F53" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="78"/>
+      <c r="B54" s="78"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="57" t="s">
+        <v>354</v>
+      </c>
+      <c r="E54" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F54" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="78"/>
+      <c r="B55" s="78"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="E55" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F55" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="78"/>
+      <c r="B56" s="78"/>
+      <c r="C56" s="78"/>
+      <c r="D56" s="57" t="s">
+        <v>356</v>
+      </c>
+      <c r="E56" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F56" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="76"/>
+      <c r="B57" s="76"/>
+      <c r="C57" s="76"/>
+      <c r="D57" s="57" t="s">
+        <v>357</v>
+      </c>
+      <c r="E57" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F57" s="57" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="59"/>
+      <c r="B58" s="59"/>
+      <c r="C58" s="59"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A53:A57"/>
+    <mergeCell ref="B53:B57"/>
+    <mergeCell ref="C53:C57"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E021E14-FAD3-4A17-B4C1-7777A30382D2}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="60" t="s">
+        <v>443</v>
+      </c>
+      <c r="B1" s="60" t="s">
+        <v>444</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>445</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>446</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C4" s="68"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB9E7CC-4D14-44C3-BBD5-A2B5D359D08B}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="69" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="71"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="54" t="s">
+        <v>450</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>451</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>452</v>
+      </c>
+      <c r="E2" s="54" t="s">
+        <v>453</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>454</v>
+      </c>
+      <c r="G2" s="54" t="s">
+        <v>455</v>
+      </c>
+      <c r="H2" s="54" t="s">
+        <v>456</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="72" t="s">
+        <v>458</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>459</v>
+      </c>
+      <c r="C3" s="62">
+        <v>5</v>
+      </c>
+      <c r="D3" s="63">
+        <v>5</v>
+      </c>
+      <c r="E3" s="63">
+        <v>0</v>
+      </c>
+      <c r="F3" s="62">
+        <v>5</v>
+      </c>
+      <c r="G3" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H3" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I3" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="73"/>
+      <c r="B4" s="61" t="s">
+        <v>462</v>
+      </c>
+      <c r="C4" s="62">
+        <v>1</v>
+      </c>
+      <c r="D4" s="63">
+        <v>1</v>
+      </c>
+      <c r="E4" s="63">
+        <v>0</v>
+      </c>
+      <c r="F4" s="62">
+        <v>1</v>
+      </c>
+      <c r="G4" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H4" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I4" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="73"/>
+      <c r="B5" s="61" t="s">
+        <v>463</v>
+      </c>
+      <c r="C5" s="62">
+        <v>3</v>
+      </c>
+      <c r="D5" s="63">
+        <v>3</v>
+      </c>
+      <c r="E5" s="63">
+        <v>0</v>
+      </c>
+      <c r="F5" s="62">
+        <v>3</v>
+      </c>
+      <c r="G5" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H5" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I5" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="73"/>
+      <c r="B6" s="61" t="s">
+        <v>464</v>
+      </c>
+      <c r="C6" s="62">
+        <v>1</v>
+      </c>
+      <c r="D6" s="63">
+        <v>1</v>
+      </c>
+      <c r="E6" s="63">
+        <v>0</v>
+      </c>
+      <c r="F6" s="62">
+        <v>1</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H6" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I6" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="73"/>
+      <c r="B7" s="61" t="s">
+        <v>465</v>
+      </c>
+      <c r="C7" s="62">
+        <v>4</v>
+      </c>
+      <c r="D7" s="63">
+        <v>4</v>
+      </c>
+      <c r="E7" s="63">
+        <v>0</v>
+      </c>
+      <c r="F7" s="62">
+        <v>4</v>
+      </c>
+      <c r="G7" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H7" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I7" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="73"/>
+      <c r="B8" s="61" t="s">
+        <v>363</v>
+      </c>
+      <c r="C8" s="62">
+        <v>3</v>
+      </c>
+      <c r="D8" s="63">
+        <v>3</v>
+      </c>
+      <c r="E8" s="63">
+        <v>0</v>
+      </c>
+      <c r="F8" s="62">
+        <v>3</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H8" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I8" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="73"/>
+      <c r="B9" s="61" t="s">
+        <v>369</v>
+      </c>
+      <c r="C9" s="62">
+        <v>1</v>
+      </c>
+      <c r="D9" s="63">
+        <v>1</v>
+      </c>
+      <c r="E9" s="63">
+        <v>0</v>
+      </c>
+      <c r="F9" s="62">
+        <v>1</v>
+      </c>
+      <c r="G9" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H9" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I9" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="73"/>
+      <c r="B10" s="61" t="s">
+        <v>466</v>
+      </c>
+      <c r="C10" s="62">
+        <v>3</v>
+      </c>
+      <c r="D10" s="63">
+        <v>3</v>
+      </c>
+      <c r="E10" s="63">
+        <v>0</v>
+      </c>
+      <c r="F10" s="62">
+        <v>3</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H10" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I10" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="73"/>
+      <c r="B11" s="61" t="s">
+        <v>467</v>
+      </c>
+      <c r="C11" s="62">
+        <v>3</v>
+      </c>
+      <c r="D11" s="63">
+        <v>3</v>
+      </c>
+      <c r="E11" s="63">
+        <v>0</v>
+      </c>
+      <c r="F11" s="62">
+        <v>3</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H11" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I11" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="73"/>
+      <c r="B12" s="61" t="s">
+        <v>468</v>
+      </c>
+      <c r="C12" s="62">
+        <v>3</v>
+      </c>
+      <c r="D12" s="63">
+        <v>3</v>
+      </c>
+      <c r="E12" s="63">
+        <v>0</v>
+      </c>
+      <c r="F12" s="62">
+        <v>3</v>
+      </c>
+      <c r="G12" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H12" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I12" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="73"/>
+      <c r="B13" s="61" t="s">
+        <v>469</v>
+      </c>
+      <c r="C13" s="62">
+        <v>2</v>
+      </c>
+      <c r="D13" s="63">
+        <v>0</v>
+      </c>
+      <c r="E13" s="63">
+        <v>0</v>
+      </c>
+      <c r="F13" s="62">
+        <v>2</v>
+      </c>
+      <c r="G13" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H13" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I13" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="73"/>
+      <c r="B14" s="61" t="s">
+        <v>470</v>
+      </c>
+      <c r="C14" s="62">
+        <v>2</v>
+      </c>
+      <c r="D14" s="63">
+        <v>2</v>
+      </c>
+      <c r="E14" s="63">
+        <v>0</v>
+      </c>
+      <c r="F14" s="62">
+        <v>2</v>
+      </c>
+      <c r="G14" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H14" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I14" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="73"/>
+      <c r="B15" s="61" t="s">
+        <v>471</v>
+      </c>
+      <c r="C15" s="62">
+        <v>3</v>
+      </c>
+      <c r="D15" s="63">
+        <v>3</v>
+      </c>
+      <c r="E15" s="63">
+        <v>0</v>
+      </c>
+      <c r="F15" s="62">
+        <v>3</v>
+      </c>
+      <c r="G15" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H15" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="73"/>
+      <c r="B16" s="61" t="s">
+        <v>472</v>
+      </c>
+      <c r="C16" s="62">
+        <v>3</v>
+      </c>
+      <c r="D16" s="63">
+        <v>3</v>
+      </c>
+      <c r="E16" s="63">
+        <v>0</v>
+      </c>
+      <c r="F16" s="62">
+        <v>3</v>
+      </c>
+      <c r="G16" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H16" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I16" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="74"/>
+      <c r="B17" s="61" t="s">
+        <v>473</v>
+      </c>
+      <c r="C17" s="62">
+        <v>5</v>
+      </c>
+      <c r="D17" s="63">
+        <v>5</v>
+      </c>
+      <c r="E17" s="63">
+        <v>0</v>
+      </c>
+      <c r="F17" s="62">
+        <v>5</v>
+      </c>
+      <c r="G17" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H17" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I17" s="64" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="60" t="s">
+        <v>474</v>
+      </c>
+      <c r="B18" s="65"/>
+      <c r="C18" s="66">
+        <v>42</v>
+      </c>
+      <c r="D18" s="67">
+        <v>42</v>
+      </c>
+      <c r="E18" s="63">
+        <v>0</v>
+      </c>
+      <c r="F18" s="66">
+        <v>42</v>
+      </c>
+      <c r="G18" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="H18" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="I18" s="67" t="s">
+        <v>460</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:A17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>